--- a/outputs_xlsx_solution/test_new3.2-wide.xlsx
+++ b/outputs_xlsx_solution/test_new3.2-wide.xlsx
@@ -65,7 +65,7 @@
     <t>addi X4, X0, 4</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>fld F1, 0(X1)</t>
@@ -74,10 +74,10 @@
     <t>fadd F2, F1, F1</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>fadd F3, F1, F1</t>
@@ -86,6 +86,9 @@
     <t>fmul F3, F3, F1</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>fadd F4, F1, F1</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
     <t>fsd F4, 0(X1)</t>
   </si>
   <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
     <t>add X1, X1, X4</t>
   </si>
   <si>
@@ -125,13 +131,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -642,7 +666,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -665,10 +689,10 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -691,10 +715,10 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -717,10 +741,10 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +770,7 @@
         <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -766,19 +790,19 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -798,19 +822,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -830,22 +854,22 @@
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -856,7 +880,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -868,19 +892,19 @@
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N10" t="s">
         <v>13</v>
       </c>
       <c r="Q10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -891,7 +915,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -899,20 +923,29 @@
       <c r="I11" t="s">
         <v>7</v>
       </c>
+      <c r="J11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
       <c r="L11" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="s">
         <v>13</v>
+      </c>
+      <c r="R11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -932,22 +965,22 @@
         <v>7</v>
       </c>
       <c r="L12" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -958,7 +991,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -967,16 +1000,16 @@
         <v>7</v>
       </c>
       <c r="M13" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R13" t="s">
         <v>13</v>
       </c>
       <c r="U13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -987,7 +1020,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J14" t="s">
         <v>5</v>
@@ -1001,8 +1034,8 @@
       <c r="N14" t="s">
         <v>13</v>
       </c>
-      <c r="U14" t="s">
-        <v>13</v>
+      <c r="V14" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1013,7 +1046,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J15" t="s">
         <v>5</v>
@@ -1027,8 +1060,8 @@
       <c r="O15" t="s">
         <v>13</v>
       </c>
-      <c r="U15" t="s">
-        <v>13</v>
+      <c r="V15" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -1039,7 +1072,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1048,16 +1081,16 @@
         <v>7</v>
       </c>
       <c r="N16" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P16" t="s">
         <v>13</v>
       </c>
-      <c r="U16" t="s">
-        <v>13</v>
+      <c r="W16" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1068,7 +1101,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -1077,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="O17" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="s">
         <v>13</v>
       </c>
-      <c r="U17" t="s">
-        <v>13</v>
+      <c r="W17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -1097,7 +1130,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q18" t="s">
         <v>5</v>
@@ -1109,13 +1142,16 @@
         <v>10</v>
       </c>
       <c r="T18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V18" t="s">
         <v>13</v>
+      </c>
+      <c r="X18" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1135,22 +1171,22 @@
         <v>7</v>
       </c>
       <c r="S19" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="U19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -1161,7 +1197,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R20" t="s">
         <v>5</v>
@@ -1170,16 +1206,16 @@
         <v>7</v>
       </c>
       <c r="T20" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V20" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W20" t="s">
         <v>13</v>
       </c>
       <c r="Y20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -1190,7 +1226,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R21" t="s">
         <v>5</v>
@@ -1199,16 +1235,16 @@
         <v>7</v>
       </c>
       <c r="T21" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="U21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V21" t="s">
         <v>13</v>
       </c>
-      <c r="Y21" t="s">
-        <v>13</v>
+      <c r="Z21" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1219,7 +1255,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="S22" t="s">
         <v>5</v>
@@ -1228,16 +1264,16 @@
         <v>7</v>
       </c>
       <c r="U22" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W22" t="s">
         <v>13</v>
       </c>
-      <c r="Y22" t="s">
-        <v>13</v>
+      <c r="Z22" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1248,7 +1284,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S23" t="s">
         <v>5</v>
@@ -1257,56 +1293,56 @@
         <v>7</v>
       </c>
       <c r="U23" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W23" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X23" t="s">
         <v>13</v>
       </c>
-      <c r="Y23" t="s">
-        <v>13</v>
+      <c r="AA23" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="T24" t="s">
+        <v>5</v>
       </c>
       <c r="U24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V24" t="s">
-        <v>7</v>
-      </c>
-      <c r="W24" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X24" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="U25" t="s">
         <v>5</v>
@@ -1315,59 +1351,65 @@
         <v>7</v>
       </c>
       <c r="W25" t="s">
+        <v>17</v>
+      </c>
+      <c r="X25" t="s">
         <v>10</v>
       </c>
       <c r="Y25" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB25" t="s">
         <v>14</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="U26" t="s">
+        <v>5</v>
       </c>
       <c r="V26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="s">
-        <v>7</v>
-      </c>
-      <c r="X26" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="s">
         <v>10</v>
       </c>
       <c r="Z26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA26" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>10</v>
       </c>
       <c r="AC26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
@@ -1379,56 +1421,56 @@
         <v>7</v>
       </c>
       <c r="X27" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z27" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB27" t="s">
         <v>13</v>
       </c>
       <c r="AC27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="V28" t="s">
+        <v>5</v>
       </c>
       <c r="W28" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X28" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Y28" t="s">
         <v>10</v>
       </c>
       <c r="Z28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W29" t="s">
         <v>5</v>
@@ -1437,560 +1479,686 @@
         <v>7</v>
       </c>
       <c r="Y29" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z29" t="s">
         <v>10</v>
       </c>
       <c r="AA29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>24</v>
+      </c>
+      <c r="W30" t="s">
+        <v>5</v>
+      </c>
+      <c r="X30" t="s">
+        <v>7</v>
       </c>
       <c r="Y30" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="s">
         <v>10</v>
       </c>
       <c r="AB30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="X31" t="s">
+        <v>5</v>
       </c>
       <c r="Y31" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA31" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB31" t="s">
         <v>10</v>
       </c>
       <c r="AC31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="s">
         <v>14</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
       </c>
+      <c r="Y32" t="s">
+        <v>5</v>
+      </c>
       <c r="Z32" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AB32" t="s">
         <v>10</v>
       </c>
+      <c r="AC32" t="s">
+        <v>10</v>
+      </c>
       <c r="AD32" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE32" t="s">
         <v>13</v>
       </c>
-      <c r="AG32" t="s">
-        <v>13</v>
+      <c r="AF32" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>5</v>
       </c>
       <c r="Z33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AC33" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AD33" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>10</v>
       </c>
       <c r="AG33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>5</v>
       </c>
       <c r="AA34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB34" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE34" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF34" t="s">
         <v>13</v>
       </c>
       <c r="AG34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
       </c>
+      <c r="Z35" t="s">
+        <v>5</v>
+      </c>
       <c r="AA35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB35" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC35" t="s">
         <v>10</v>
       </c>
-      <c r="AE35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>13</v>
+      <c r="AD35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>7</v>
       </c>
       <c r="AC36" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AD36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE36" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>24</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>7</v>
       </c>
       <c r="AC37" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AE37" t="s">
         <v>10</v>
       </c>
-      <c r="AG37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH37" t="s">
-        <v>14</v>
+      <c r="AF37" t="s">
+        <v>13</v>
       </c>
       <c r="AI37" t="s">
         <v>14</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>7</v>
       </c>
       <c r="AD38" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AF38" t="s">
         <v>10</v>
       </c>
-      <c r="AH38" t="s">
-        <v>14</v>
+      <c r="AG38" t="s">
+        <v>13</v>
       </c>
       <c r="AI38" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>5</v>
       </c>
       <c r="AD39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE39" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AF39" t="s">
         <v>10</v>
       </c>
       <c r="AG39" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AH39" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>7</v>
       </c>
       <c r="AE40" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AG40" t="s">
         <v>10</v>
       </c>
       <c r="AH40" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI40" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>10</v>
       </c>
       <c r="AK40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>5</v>
       </c>
       <c r="AE41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF41" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AI41" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AJ41" t="s">
         <v>13</v>
       </c>
       <c r="AK41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>7</v>
       </c>
       <c r="AF42" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AG42" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AH42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK43" t="s">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>13</v>
       </c>
       <c r="AL43" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM43" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL44" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>13</v>
       </c>
       <c r="AM44" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
         <v>25</v>
       </c>
-      <c r="AL45" t="s">
-        <v>5</v>
+      <c r="AF45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>13</v>
       </c>
       <c r="AM45" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN45" t="s">
-        <v>10</v>
-      </c>
-      <c r="AP45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
         <v>26</v>
       </c>
+      <c r="AK46" t="s">
+        <v>5</v>
+      </c>
       <c r="AL46" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM46" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AN46" t="s">
         <v>10</v>
       </c>
-      <c r="AQ46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR46" t="s">
-        <v>13</v>
+      <c r="AO46" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO47" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP47" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ47" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>72</v>
+      </c>
+      <c r="C48" t="s">
         <v>27</v>
       </c>
+      <c r="AL48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP48" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ48" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>76</v>
+      </c>
+      <c r="C49" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" t="s">
-        <v>29</v>
+      <c r="AL49" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM49" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ49" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR49" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test_new3.2-wide.xlsx
+++ b/outputs_xlsx_solution/test_new3.2-wide.xlsx
@@ -68,6 +68,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fld F1, 0(X1)</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -666,7 +672,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -686,13 +692,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -712,13 +718,13 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -738,13 +744,16 @@
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +764,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -767,10 +776,10 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +790,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -790,7 +799,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
@@ -802,7 +811,7 @@
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -813,7 +822,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
@@ -822,7 +831,7 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J8" t="s">
         <v>10</v>
@@ -834,7 +843,7 @@
         <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -845,7 +854,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
@@ -854,7 +863,7 @@
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
         <v>10</v>
@@ -869,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -880,7 +889,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -889,7 +898,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="s">
         <v>10</v>
@@ -901,10 +910,10 @@
         <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -915,7 +924,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -924,13 +933,13 @@
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11" t="s">
         <v>10</v>
@@ -942,10 +951,10 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -956,7 +965,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
         <v>5</v>
@@ -965,7 +974,7 @@
         <v>7</v>
       </c>
       <c r="L12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="s">
         <v>10</v>
@@ -980,7 +989,7 @@
         <v>10</v>
       </c>
       <c r="U12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -991,7 +1000,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -1000,16 +1009,16 @@
         <v>7</v>
       </c>
       <c r="M13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="s">
         <v>10</v>
       </c>
       <c r="R13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1020,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
         <v>5</v>
@@ -1032,10 +1041,10 @@
         <v>10</v>
       </c>
       <c r="N14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1046,7 +1055,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
         <v>5</v>
@@ -1058,10 +1067,10 @@
         <v>10</v>
       </c>
       <c r="O15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1072,7 +1081,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1081,16 +1090,16 @@
         <v>7</v>
       </c>
       <c r="N16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O16" t="s">
         <v>10</v>
       </c>
       <c r="P16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1101,7 +1110,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -1110,16 +1119,16 @@
         <v>7</v>
       </c>
       <c r="O17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P17" t="s">
         <v>10</v>
       </c>
       <c r="Q17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1130,7 +1139,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="s">
         <v>5</v>
@@ -1148,10 +1157,10 @@
         <v>10</v>
       </c>
       <c r="V18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1162,7 +1171,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="s">
         <v>5</v>
@@ -1171,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="S19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U19" t="s">
         <v>10</v>
@@ -1186,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="Y19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1197,7 +1206,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R20" t="s">
         <v>5</v>
@@ -1206,16 +1215,16 @@
         <v>7</v>
       </c>
       <c r="T20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V20" t="s">
         <v>10</v>
       </c>
       <c r="W20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1226,7 +1235,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R21" t="s">
         <v>5</v>
@@ -1235,16 +1244,16 @@
         <v>7</v>
       </c>
       <c r="T21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U21" t="s">
         <v>10</v>
       </c>
       <c r="V21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1255,7 +1264,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S22" t="s">
         <v>5</v>
@@ -1264,16 +1273,16 @@
         <v>7</v>
       </c>
       <c r="U22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V22" t="s">
         <v>10</v>
       </c>
       <c r="W22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1284,7 +1293,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S23" t="s">
         <v>5</v>
@@ -1293,16 +1302,16 @@
         <v>7</v>
       </c>
       <c r="U23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W23" t="s">
         <v>10</v>
       </c>
       <c r="X23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1313,7 +1322,7 @@
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T24" t="s">
         <v>5</v>
@@ -1322,16 +1331,16 @@
         <v>7</v>
       </c>
       <c r="V24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X24" t="s">
         <v>10</v>
       </c>
       <c r="Y24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1342,7 +1351,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U25" t="s">
         <v>5</v>
@@ -1351,7 +1360,7 @@
         <v>7</v>
       </c>
       <c r="W25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X25" t="s">
         <v>10</v>
@@ -1363,10 +1372,10 @@
         <v>10</v>
       </c>
       <c r="AA25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1377,7 +1386,7 @@
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U26" t="s">
         <v>5</v>
@@ -1386,7 +1395,7 @@
         <v>7</v>
       </c>
       <c r="W26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y26" t="s">
         <v>10</v>
@@ -1401,7 +1410,7 @@
         <v>10</v>
       </c>
       <c r="AC26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1412,7 +1421,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V27" t="s">
         <v>5</v>
@@ -1421,16 +1430,16 @@
         <v>7</v>
       </c>
       <c r="X27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="s">
         <v>10</v>
       </c>
       <c r="AB27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1441,7 +1450,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V28" t="s">
         <v>5</v>
@@ -1450,16 +1459,16 @@
         <v>7</v>
       </c>
       <c r="X28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y28" t="s">
         <v>10</v>
       </c>
       <c r="Z28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1470,7 +1479,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W29" t="s">
         <v>5</v>
@@ -1479,16 +1488,16 @@
         <v>7</v>
       </c>
       <c r="Y29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z29" t="s">
         <v>10</v>
       </c>
       <c r="AA29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1499,7 +1508,7 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W30" t="s">
         <v>5</v>
@@ -1508,16 +1517,16 @@
         <v>7</v>
       </c>
       <c r="Y30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA30" t="s">
         <v>10</v>
       </c>
       <c r="AB30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1528,7 +1537,7 @@
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X31" t="s">
         <v>5</v>
@@ -1537,16 +1546,16 @@
         <v>7</v>
       </c>
       <c r="Z31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB31" t="s">
         <v>10</v>
       </c>
       <c r="AC31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1557,7 +1566,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s">
         <v>5</v>
@@ -1566,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="AA32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB32" t="s">
         <v>10</v>
@@ -1578,10 +1587,10 @@
         <v>10</v>
       </c>
       <c r="AE32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1592,7 +1601,7 @@
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y33" t="s">
         <v>5</v>
@@ -1601,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="AA33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC33" t="s">
         <v>10</v>
@@ -1616,7 +1625,7 @@
         <v>10</v>
       </c>
       <c r="AG33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -1627,7 +1636,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s">
         <v>5</v>
@@ -1636,16 +1645,16 @@
         <v>7</v>
       </c>
       <c r="AB34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE34" t="s">
         <v>10</v>
       </c>
       <c r="AF34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1656,7 +1665,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z35" t="s">
         <v>5</v>
@@ -1665,16 +1674,16 @@
         <v>7</v>
       </c>
       <c r="AB35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC35" t="s">
         <v>10</v>
       </c>
       <c r="AD35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1685,7 +1694,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA36" t="s">
         <v>5</v>
@@ -1694,16 +1703,16 @@
         <v>7</v>
       </c>
       <c r="AC36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD36" t="s">
         <v>10</v>
       </c>
       <c r="AE36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1714,7 +1723,7 @@
         <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA37" t="s">
         <v>5</v>
@@ -1723,16 +1732,16 @@
         <v>7</v>
       </c>
       <c r="AC37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE37" t="s">
         <v>10</v>
       </c>
       <c r="AF37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1743,7 +1752,7 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB38" t="s">
         <v>5</v>
@@ -1752,16 +1761,16 @@
         <v>7</v>
       </c>
       <c r="AD38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF38" t="s">
         <v>10</v>
       </c>
       <c r="AG38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1772,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC39" t="s">
         <v>5</v>
@@ -1781,7 +1790,7 @@
         <v>7</v>
       </c>
       <c r="AE39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF39" t="s">
         <v>10</v>
@@ -1793,10 +1802,10 @@
         <v>10</v>
       </c>
       <c r="AI39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -1807,7 +1816,7 @@
         <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC40" t="s">
         <v>5</v>
@@ -1816,7 +1825,7 @@
         <v>7</v>
       </c>
       <c r="AE40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG40" t="s">
         <v>10</v>
@@ -1831,7 +1840,7 @@
         <v>10</v>
       </c>
       <c r="AK40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1842,7 +1851,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD41" t="s">
         <v>5</v>
@@ -1851,16 +1860,16 @@
         <v>7</v>
       </c>
       <c r="AF41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI41" t="s">
         <v>10</v>
       </c>
       <c r="AJ41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -1871,7 +1880,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD42" t="s">
         <v>5</v>
@@ -1880,16 +1889,16 @@
         <v>7</v>
       </c>
       <c r="AF42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG42" t="s">
         <v>10</v>
       </c>
       <c r="AH42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -1900,7 +1909,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE43" t="s">
         <v>5</v>
@@ -1909,16 +1918,16 @@
         <v>7</v>
       </c>
       <c r="AG43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH43" t="s">
         <v>10</v>
       </c>
       <c r="AI43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -1929,7 +1938,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE44" t="s">
         <v>5</v>
@@ -1938,16 +1947,16 @@
         <v>7</v>
       </c>
       <c r="AG44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI44" t="s">
         <v>10</v>
       </c>
       <c r="AJ44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -1958,7 +1967,7 @@
         <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF45" t="s">
         <v>5</v>
@@ -1967,16 +1976,16 @@
         <v>7</v>
       </c>
       <c r="AH45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ45" t="s">
         <v>10</v>
       </c>
       <c r="AK45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -1987,7 +1996,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK46" t="s">
         <v>5</v>
@@ -2005,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="AP46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -2016,7 +2025,7 @@
         <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK47" t="s">
         <v>5</v>
@@ -2037,7 +2046,7 @@
         <v>10</v>
       </c>
       <c r="AQ47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -2048,7 +2057,7 @@
         <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL48" t="s">
         <v>5</v>
@@ -2057,13 +2066,13 @@
         <v>7</v>
       </c>
       <c r="AN48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP48" t="s">
         <v>10</v>
       </c>
       <c r="AQ48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -2074,7 +2083,7 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL49" t="s">
         <v>5</v>
@@ -2083,18 +2092,18 @@
         <v>7</v>
       </c>
       <c r="AN49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ49" t="s">
         <v>10</v>
       </c>
       <c r="AR49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -2102,7 +2111,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
@@ -2110,15 +2119,15 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -2126,39 +2135,55 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" t="s">
         <v>39</v>
       </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
